--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91826</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130190075</v>
       </c>
       <c r="B5" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91915</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130190075</v>
       </c>
       <c r="B5" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91944</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190078</v>
       </c>
       <c r="B2" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190080</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190081</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130190075</v>
       </c>
       <c r="B5" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130190078</v>
+        <v>130190080</v>
       </c>
       <c r="B2" t="n">
-        <v>91948</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761298</v>
+        <v>761239</v>
       </c>
       <c r="R2" t="n">
-        <v>7103495</v>
+        <v>7103434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130190080</v>
+        <v>130190078</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>92097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761239</v>
+        <v>761298</v>
       </c>
       <c r="R3" t="n">
-        <v>7103434</v>
+        <v>7103495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,30 +899,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190081</v>
+        <v>130190075</v>
       </c>
       <c r="B4" t="n">
-        <v>91781</v>
+        <v>44177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,7 +934,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761274</v>
+        <v>761176</v>
       </c>
       <c r="R4" t="n">
         <v>7103428</v>
@@ -965,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1004,118 +1008,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>130190075</v>
-      </c>
-      <c r="B5" t="n">
-        <v>44108</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>101735</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Jättesvampmal</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Scardia boletella</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Skellefteå-Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>761176</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7103428</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>NVI (C250260) Calluna AB</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Jonas Mattsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12971-2025 artfynd.xlsx
+++ b/artfynd/A 12971-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190078</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,8 +1023,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>